--- a/04_DESIGN_TABLES/DesignTable_5406P.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5406P.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -511,6 +511,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -667,7 +672,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>5406-8P</t>
+          <t>5406-08P</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -677,7 +682,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -687,12 +692,17 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-18: BUILD - the DROP above is void: OMi sells 5406-P-08 (alias of this Air-Way row, A4) | Brennan TFA p.67 TFA-p067-t03 row 5406-P-08: L2@DRIVE Air-Way 0.96 vs Brennan L LGTH 0.960: equal; C2HEX@HEX Air-Way 0.88 vs Brennan C HEX 0.875: rounding only</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5406-P-08</t>
         </is>
       </c>
     </row>
@@ -733,12 +743,17 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-18: BUILD - the DROP above is void: OMi sells 5406-P-12 (alias of this Air-Way row, A4) | Brennan TFA p.67 TFA-p067-t03 row 5406-P-12: L2@DRIVE Air-Way 1.05 vs Brennan L LGTH 1.170: DIFFERS (Air-Way kept, s6); C2HEX@HEX Air-Way 1.13 vs Brennan C HEX 1.125: rounding only</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>5406-P-12</t>
         </is>
       </c>
     </row>
@@ -936,24 +951,38 @@
           <t>5406-P-02</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.405</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>5406-P-02</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1/8-27 NPTF male plug</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L2@DRIVE: Brennan TFA catalog p67 table TFA-p067-t03 (EXTERNAL HEX PIPE PLUG) row 5406-P-02 column 'L LGTH' = 0.562 (catalog_verified.json); OMi Items row 1416: no dimension; Air-Way prints this size only as 5406-02P (review row, DROP; alias = Q-NEW-AWALIAS, open) = 0.56, rounding-only equal; 2026-10-02 proposal used the Air-Way alias value 0.56 - Brennan as printed is used here (alias not settled); C2HEX@HEX: Brennan TFA catalog p67 table TFA-p067-t03 (EXTERNAL HEX PIPE PLUG) row 5406-P-02 column 'C HEX' = 0.438 (catalog_verified.json); OMi Items row 1416: no dimension; Air-Way prints this size only as 5406-02P (review row, DROP; alias = Q-NEW-AWALIAS, open) = 0.44, rounding-only equal; 2026-10-02 proposal used the Air-Way alias value 0.44 - Brennan as printed is used here (alias not settled); THDMAJ_A@DRIVE: ASME B1.20.1 / B1.20.3 1/8 NPT basic dimensions = tools_new/generators/ms51500.NPTF[2] pipe OD (= alias row 5406-02P 0.405); equals the 2026-10-02 proposal; $PRP@Threads: ASME B1.20.1 / B1.20.3 1/8 NPT basic dimensions = tools_new/generators/ms51500.NPTF[2] thread text, format of the 5406P rows; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): L2 / hex from the Brennan TFA catalog alone (Air-Way alias 5406-02P agrees to rounding; alias not yet confirmed - Q-NEW-AWALIAS)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -964,6 +993,11 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>5406-P-02</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -973,24 +1007,38 @@
           <t>5406-P-04</t>
         </is>
       </c>
+      <c r="B13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.54</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>5406-P-04</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF male plug</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L2@DRIVE: Brennan TFA catalog p67 table TFA-p067-t03 (EXTERNAL HEX PIPE PLUG) row 5406-P-04 column 'L LGTH' = 0.750 (catalog_verified.json); OMi Items row 1417: no dimension; Air-Way prints this size only as 5406-04P (review row, DROP; alias = Q-NEW-AWALIAS, open) = 0.75, rounding-only equal; 2026-10-02 proposal used the Air-Way alias value 0.75 - Brennan as printed is used here (alias not settled); C2HEX@HEX: Brennan TFA catalog p67 table TFA-p067-t03 (EXTERNAL HEX PIPE PLUG) row 5406-P-04 column 'C HEX' = 0.562 (catalog_verified.json); OMi Items row 1417: no dimension; Air-Way prints this size only as 5406-04P (review row, DROP; alias = Q-NEW-AWALIAS, open) = 0.56, rounding-only equal; 2026-10-02 proposal used the Air-Way alias value 0.56 - Brennan as printed is used here (alias not settled); THDMAJ_A@DRIVE: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] pipe OD (= alias row 5406-04P 0.54); equals the 2026-10-02 proposal; $PRP@Threads: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] thread text, format of the 5406P rows; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): L2 / hex from the Brennan TFA catalog alone (Air-Way alias 5406-04P agrees to rounding; alias not yet confirmed - Q-NEW-AWALIAS)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1001,6 +1049,11 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>5406-P-04</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1010,24 +1063,38 @@
           <t>5406-P-06</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.675</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>5406-P-06</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF male plug</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L2@DRIVE: Brennan TFA catalog p67 table TFA-p067-t03 (EXTERNAL HEX PIPE PLUG) row 5406-P-06 column 'L LGTH' = 0.780 (catalog_verified.json); OMi Items row 1418: no dimension; Air-Way prints this size only as 5406-06P (review row, DROP; alias = Q-NEW-AWALIAS, open) = 0.78, rounding-only equal; 2026-10-02 proposal used the Air-Way alias value 0.78 - Brennan as printed is used here (alias not settled); C2HEX@HEX: Brennan TFA catalog p67 table TFA-p067-t03 (EXTERNAL HEX PIPE PLUG) row 5406-P-06 column 'C HEX' = 0.688 (catalog_verified.json); OMi Items row 1418: no dimension; Air-Way prints this size only as 5406-06P (review row, DROP; alias = Q-NEW-AWALIAS, open) = 0.69, rounding-only equal; 2026-10-02 proposal used the Air-Way alias value 0.69 - Brennan as printed is used here (alias not settled); THDMAJ_A@DRIVE: ASME B1.20.1 / B1.20.3 3/8 NPT basic dimensions = tools_new/generators/ms51500.NPTF[6] pipe OD (= alias row 5406-06P 0.675); equals the 2026-10-02 proposal; $PRP@Threads: ASME B1.20.1 / B1.20.3 3/8 NPT basic dimensions = tools_new/generators/ms51500.NPTF[6] thread text, format of the 5406P rows; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): L2 / hex from the Brennan TFA catalog alone (Air-Way alias 5406-06P agrees to rounding; alias not yet confirmed - Q-NEW-AWALIAS)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1038,6 +1105,11 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>5406-P-06</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
